--- a/Q4_结果.xlsx
+++ b/Q4_结果.xlsx
@@ -17,8 +17,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Q4_分区配置'!$A$1:$K$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'分组工作量'!$A$1:$J$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'库存_缺口_冗余'!$A$1:$H$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'备选方案比较'!$A$1:$G$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'必须同组的服务区'!$A$1:$B$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'备选方案比较'!$A$1:$G$122</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'必须同组的服务区'!$A$1:$B$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -494,26 +494,26 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>S001,S003,S004,S005,S006,S007,S008,S009,S011,S015</t>
+          <t>S002,S004,S005,S006,S008,S009,S010,S012,S013,S014</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
         <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J2" t="n">
         <v>2</v>
@@ -533,26 +533,26 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>S002,S010,S012,S013,S014</t>
+          <t>S001,S003,S007,S011,S015</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
@@ -572,26 +572,26 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>S001,S003,S004,S005,S007,S008,S009,S011,S015</t>
+          <t>S002,S004,S005,S006,S008,S009,S010,S012,S013,S014</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
         <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J4" t="n">
         <v>2</v>
@@ -611,23 +611,23 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>S002,S010,S012,S013,S014</t>
+          <t>S003,S007,S011,S015</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -650,7 +650,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>S006</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -660,7 +660,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -669,7 +669,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -756,29 +756,29 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>S001,S003,S004,S005,S006,S007,S008,S009,S011,S015</t>
+          <t>S002,S004,S005,S006,S008,S009,S010,S012,S013,S014</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="E2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F2" t="n">
         <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>25171.94925738256</v>
+        <v>24614.57393905928</v>
       </c>
       <c r="H2" t="n">
-        <v>36097.69018881291</v>
+        <v>33516.57735403036</v>
       </c>
       <c r="I2" t="n">
-        <v>46.09607370923445</v>
+        <v>43.32758253317756</v>
       </c>
       <c r="J2" t="n">
-        <v>3.157945489906826</v>
+        <v>2.555759247213566</v>
       </c>
     </row>
     <row r="3">
@@ -792,11 +792,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>S002,S010,S012,S013,S014</t>
+          <t>S001,S003,S007,S011,S015</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E3" t="n">
         <v>8</v>
@@ -805,16 +805,16 @@
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>15823.13906430175</v>
+        <v>13870.49414541446</v>
       </c>
       <c r="H3" t="n">
-        <v>19911.67386570401</v>
+        <v>19106.13307925469</v>
       </c>
       <c r="I3" t="n">
-        <v>23.70192962502578</v>
+        <v>21.29767626953941</v>
       </c>
       <c r="J3" t="n">
-        <v>1.151293863249245</v>
+        <v>1.499014867821895</v>
       </c>
     </row>
     <row r="4">
@@ -828,11 +828,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>S001,S003,S004,S005,S007,S008,S009,S011,S015</t>
+          <t>S002,S004,S005,S006,S008,S009,S010,S012,S013,S014</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="E4" t="n">
         <v>13</v>
@@ -841,16 +841,16 @@
         <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>23611.0853721086</v>
+        <v>24614.57393905928</v>
       </c>
       <c r="H4" t="n">
-        <v>34536.82630353895</v>
+        <v>33516.57735403036</v>
       </c>
       <c r="I4" t="n">
-        <v>43.36392685458345</v>
+        <v>43.32758253317756</v>
       </c>
       <c r="J4" t="n">
-        <v>3.157945489906826</v>
+        <v>2.555759247213566</v>
       </c>
     </row>
     <row r="5">
@@ -864,29 +864,29 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>S002,S010,S012,S013,S014</t>
+          <t>S003,S007,S011,S015</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>15823.13906430175</v>
+        <v>10681.64066201737</v>
       </c>
       <c r="H5" t="n">
-        <v>19911.67386570401</v>
+        <v>15917.27959585759</v>
       </c>
       <c r="I5" t="n">
-        <v>23.70192962502578</v>
+        <v>15.36670553370179</v>
       </c>
       <c r="J5" t="n">
-        <v>1.151293863249245</v>
+        <v>1.499014867821895</v>
       </c>
     </row>
     <row r="6">
@@ -900,26 +900,26 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>S006</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1560.863885273963</v>
+        <v>3188.853483397093</v>
       </c>
       <c r="H6" t="n">
-        <v>1560.863885273963</v>
+        <v>3188.853483397093</v>
       </c>
       <c r="I6" t="n">
-        <v>2.732146854650997</v>
+        <v>5.930970735837616</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -995,13 +995,13 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
         <v>4</v>
@@ -1051,19 +1051,19 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -1107,19 +1107,19 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1219,13 +1219,13 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
         <v>4</v>
@@ -1275,19 +1275,19 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -1331,19 +1331,19 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1442,7 +1442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1498,13 +1498,13 @@
         <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9442641811196181</v>
+        <v>0.9406771763589478</v>
       </c>
       <c r="F2" t="n">
         <v>0.85</v>
       </c>
       <c r="G2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
@@ -1523,13 +1523,13 @@
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9576256996767428</v>
+        <v>0.9547864108568602</v>
       </c>
       <c r="F3" t="n">
         <v>0.925</v>
       </c>
       <c r="G3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>S002,S003,S004,S005,S006,S007,S008,S009,S010,S011,S012,S013,S014,S015 | S001</t>
+          <t>S001,S002,S004,S005,S006,S008,S009,S010,S012,S013,S014 | S003,S007,S011,S015</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -1548,13 +1548,13 @@
         <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8861314161577264</v>
+        <v>0.3950414387705292</v>
       </c>
       <c r="F4" t="n">
-        <v>0.625</v>
+        <v>0.525</v>
       </c>
       <c r="G4" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>S001,S002,S003,S004,S005,S007,S008,S009,S010,S012,S013,S014,S015 | S006,S011</t>
+          <t>S002,S003,S004,S005,S006,S007,S008,S009,S010,S011,S012,S013,S014,S015 | S001</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1573,13 +1573,13 @@
         <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9018898807963609</v>
+        <v>0.8788031457467432</v>
       </c>
       <c r="F5" t="n">
-        <v>0.775</v>
+        <v>0.625</v>
       </c>
       <c r="G5" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6">
@@ -1588,23 +1588,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>S001,S003,S004,S005,S006,S007,S008,S009,S011,S015 | S002,S010,S012,S013,S014</t>
+          <t>S001,S002,S003,S004,S005,S007,S008,S009,S010,S012,S013,S014,S015 | S006,S011</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2889876826195381</v>
+        <v>0.895463587215808</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5</v>
+        <v>0.775</v>
       </c>
       <c r="G6" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7">
@@ -1613,23 +1613,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>S002,S003,S004,S005,S007,S008,S009,S010,S011,S012,S013,S014,S015 | S001,S006</t>
+          <t>S001,S002,S004,S005,S008,S009,S010,S012,S013,S014 | S003,S006,S007,S011,S015</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
         <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8303955972773445</v>
+        <v>0.3357186151294769</v>
       </c>
       <c r="F7" t="n">
-        <v>0.475</v>
+        <v>0.375</v>
       </c>
       <c r="G7" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8">
@@ -1638,23 +1638,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>S001,S003,S004,S005,S006,S007,S008,S009,S015 | S002,S010,S011,S012,S013,S014</t>
+          <t>S002,S004,S005,S006,S008,S009,S010,S012,S013,S014 | S001,S003,S007,S011,S015</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2466133822962809</v>
+        <v>0.2738445845172723</v>
       </c>
       <c r="F8" t="n">
-        <v>0.425</v>
+        <v>0.15</v>
       </c>
       <c r="G8" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9">
@@ -1663,23 +1663,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>S002,S003,S004,S005,S006,S007,S008,S009,S010,S012,S013,S014,S015 | S001,S011</t>
+          <t>S001,S002,S003,S004,S005,S006,S007,S008,S009,S011,S013,S015 | S010,S012,S014</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8437571158344693</v>
+        <v>0.6201170310559869</v>
       </c>
       <c r="F9" t="n">
-        <v>0.55</v>
+        <v>0.775</v>
       </c>
       <c r="G9" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10">
@@ -1688,23 +1688,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>S001,S003,S004,S005,S007,S008,S009,S011,S015 | S002,S006,S010,S012,S013,S014</t>
+          <t>S002,S003,S004,S005,S007,S008,S009,S010,S011,S012,S013,S014,S015 | S001,S006</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2332518637391562</v>
+        <v>0.8194803221056908</v>
       </c>
       <c r="F10" t="n">
-        <v>0.35</v>
+        <v>0.475</v>
       </c>
       <c r="G10" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11">
@@ -1713,23 +1713,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>S001,S003,S004,S005,S007,S008,S009,S015 | S002,S006,S010,S011,S012,S013,S014</t>
+          <t>S001,S002,S004,S005,S006,S008,S009,S013 | S003,S007,S010,S011,S012,S014,S015</t>
         </is>
       </c>
       <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="n">
         <v>6</v>
       </c>
-      <c r="D11" t="n">
-        <v>8</v>
-      </c>
       <c r="E11" t="n">
-        <v>0.1908775634158991</v>
+        <v>0.01515846982651601</v>
       </c>
       <c r="F11" t="n">
-        <v>0.275</v>
+        <v>0.3</v>
       </c>
       <c r="G11" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12">
@@ -1738,23 +1738,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>S002,S003,S004,S005,S007,S008,S009,S010,S012,S013,S014,S015 | S001,S006,S011</t>
+          <t>S001,S002,S004,S005,S008,S009,S013 | S003,S006,S007,S010,S011,S012,S014,S015</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
         <v>7</v>
       </c>
       <c r="E12" t="n">
-        <v>0.7880212969540874</v>
+        <v>0.04416435381453609</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4</v>
+        <v>0.15</v>
       </c>
       <c r="G12" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13">
@@ -1763,23 +1763,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>S003,S004,S005,S006,S007,S008,S009,S011,S015 | S001,S002,S010,S012,S013,S014</t>
+          <t>S001,S002,S004,S005,S006,S008,S009,S011,S013 | S003,S007,S010,S012,S014,S015</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
         <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1751190987772644</v>
+        <v>0.06037205896965597</v>
       </c>
       <c r="F13" t="n">
-        <v>0.125</v>
+        <v>0.375</v>
       </c>
       <c r="G13" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -1788,23 +1788,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>S003,S004,S005,S006,S007,S008,S009,S015 | S001,S002,S010,S011,S012,S013,S014</t>
+          <t>S001,S002,S004,S005,S008,S009,S011,S013 | S003,S006,S007,S010,S012,S014,S015</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
         <v>9</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1327447984540073</v>
+        <v>0.001049235328603737</v>
       </c>
       <c r="F14" t="n">
-        <v>0.05</v>
+        <v>0.225</v>
       </c>
       <c r="G14" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15">
@@ -1813,23 +1813,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>S003,S004,S005,S007,S008,S009,S011,S015 | S001,S002,S006,S010,S012,S013,S014</t>
+          <t>S002,S004,S005,S008,S009,S010,S012,S013,S014 | S001,S003,S006,S007,S011,S015</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1193832798968826</v>
+        <v>0.2145217608762201</v>
       </c>
       <c r="F15" t="n">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16">
@@ -1838,70 +1838,70 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>S003,S004,S005,S007,S008,S009,S015 | S001,S002,S006,S010,S011,S012,S013,S014</t>
+          <t>S001,S002,S004,S005,S006,S008,S009,S010,S011,S012,S013,S014 | S003,S007,S015</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E16" t="n">
-        <v>0.07700897957362546</v>
+        <v>0.4402550279136691</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="G16" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>S001,S002,S003,S004,S005,S007,S008,S009,S010,S012,S013,S014,S015 | S006 | S011</t>
+          <t>S002,S003,S004,S005,S006,S007,S008,S009,S010,S012,S013,S014,S015 | S001,S011</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E17" t="n">
-        <v>1.310177616253732</v>
+        <v>0.8335895566036032</v>
       </c>
       <c r="F17" t="n">
-        <v>1.176461856585244</v>
+        <v>0.55</v>
       </c>
       <c r="G17" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>S002,S003,S004,S005,S007,S008,S009,S010,S011,S012,S013,S014,S015 | S001 | S006</t>
+          <t>S002,S004,S005,S006,S008,S009,S013 | S001,S003,S007,S010,S011,S012,S014,S015</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E18" t="n">
-        <v>1.234834172599138</v>
+        <v>0.1060383844267408</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8683677216479202</v>
+        <v>0.075</v>
       </c>
       <c r="G18" t="n">
         <v>33</v>
@@ -1909,61 +1909,61 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>S002,S003,S004,S005,S006,S007,S008,S009,S010,S012,S013,S014,S015 | S001 | S011</t>
+          <t>S001,S002,S004,S005,S008,S009,S010,S011,S012,S013,S014 | S003,S006,S007,S015</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E19" t="n">
-        <v>1.249260362545886</v>
+        <v>0.3809322042726168</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9547578226964154</v>
+        <v>0.45</v>
       </c>
       <c r="G19" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>S001,S003,S004,S005,S007,S008,S009,S011,S015 | S002,S010,S012,S013,S014 | S006</t>
+          <t>S002,S004,S005,S006,S008,S009,S011,S013 | S001,S003,S007,S010,S012,S014,S015</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7226107993185735</v>
+        <v>0.06082479528360082</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7558108228915487</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>S001,S003,S004,S005,S006,S007,S008,S009,S015 | S002,S010,S012,S013,S014 | S011</t>
+          <t>S002,S004,S005,S006,S008,S009,S010,S011,S012,S013,S014 | S001,S003,S007,S015</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1973,22 +1973,22 @@
         <v>7</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7389413145075158</v>
+        <v>0.3190581736604123</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8453919209455457</v>
+        <v>0.225</v>
       </c>
       <c r="G21" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>S002,S003,S004,S005,S007,S008,S009,S010,S012,S013,S014,S015 | S001,S006 | S011</t>
+          <t>S001,S002,S003,S004,S005,S007,S008,S009,S011,S013,S015 | S006,S010,S012,S014</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1998,10 +1998,10 @@
         <v>7</v>
       </c>
       <c r="E22" t="n">
-        <v>1.19192535203935</v>
+        <v>0.5607942074149348</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8251893722049504</v>
+        <v>0.625</v>
       </c>
       <c r="G22" t="n">
         <v>34</v>
@@ -2009,24 +2009,24 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>S001,S003,S004,S005,S007,S008,S009,S015 | S002,S010,S011,S012,S013,S014 | S006</t>
+          <t>S001,S002,S003,S004,S005,S006,S007,S008,S009,S013,S015 | S010,S011,S012,S014</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>7</v>
       </c>
       <c r="D23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7011885881961635</v>
+        <v>0.574903441912847</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6957460025037873</v>
+        <v>0.7</v>
       </c>
       <c r="G23" t="n">
         <v>34</v>
@@ -2034,111 +2034,111 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>S002,S003,S004,S005,S007,S008,S009,S010,S012,S013,S014,S015 | S001 | S006,S011</t>
+          <t>S002,S003,S004,S005,S007,S008,S009,S010,S012,S013,S014,S015 | S001,S006,S011</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E24" t="n">
-        <v>1.189415342165356</v>
+        <v>0.774266732962551</v>
       </c>
       <c r="F24" t="n">
-        <v>0.783222509891027</v>
+        <v>0.4</v>
       </c>
       <c r="G24" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>S002,S003,S004,S005,S007,S008,S009,S010,S012,S013,S014,S015 | S001,S011 | S006</t>
+          <t>S002,S004,S005,S008,S009,S013 | S001,S003,S006,S007,S010,S011,S012,S014,S015</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D25" t="n">
         <v>8</v>
       </c>
       <c r="E25" t="n">
-        <v>1.190967614605874</v>
+        <v>0.165361208067793</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7992183681572889</v>
+        <v>0.225</v>
       </c>
       <c r="G25" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>S001,S003,S004,S005,S007,S008,S009,S015 | S002,S006,S010,S012,S013,S014 | S011</t>
+          <t>S002,S004,S005,S008,S009,S011,S013 | S001,S003,S006,S007,S010,S012,S014,S015</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E26" t="n">
-        <v>0.7112775426133345</v>
+        <v>0.1201476189246531</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7350595213994577</v>
+        <v>0.15</v>
       </c>
       <c r="G26" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>S003,S004,S005,S006,S007,S008,S009,S011,S015 | S002,S010,S012,S013,S014 | S001</t>
+          <t>S002,S004,S005,S008,S009,S010,S011,S012,S013,S014 | S001,S003,S006,S007,S015</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E27" t="n">
-        <v>0.6515804628923832</v>
+        <v>0.2597353500193599</v>
       </c>
       <c r="F27" t="n">
-        <v>0.4921254921257382</v>
+        <v>0.075</v>
       </c>
       <c r="G27" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>S001,S003,S004,S005,S007,S008,S009,S015 | S002,S010,S012,S013,S014 | S006,S011</t>
+          <t>S002,S003,S004,S005,S006,S007,S008,S009,S011,S013,S015 | S001,S010,S012,S014</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -2148,10 +2148,10 @@
         <v>9</v>
       </c>
       <c r="E28" t="n">
-        <v>0.6708316566048496</v>
+        <v>0.4989201768027301</v>
       </c>
       <c r="F28" t="n">
-        <v>0.6668489334174569</v>
+        <v>0.4</v>
       </c>
       <c r="G28" t="n">
         <v>36</v>
@@ -2159,24 +2159,24 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>S003,S004,S005,S006,S007,S008,S009,S015 | S002,S010,S011,S012,S013,S014 | S001</t>
+          <t>S001,S002,S003,S004,S005,S007,S008,S009,S013,S015 | S006,S010,S011,S012,S014</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>9</v>
       </c>
       <c r="D29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E29" t="n">
-        <v>0.6306751710741657</v>
+        <v>0.5155806182717949</v>
       </c>
       <c r="F29" t="n">
-        <v>0.4246321937865757</v>
+        <v>0.55</v>
       </c>
       <c r="G29" t="n">
         <v>36</v>
@@ -2184,11 +2184,11 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>S003,S004,S005,S007,S008,S009,S011,S015 | S002,S010,S012,S013,S014 | S001,S006</t>
+          <t>S002,S003,S004,S005,S007,S008,S009,S011,S013,S015 | S001,S006,S010,S012,S014</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -2198,10 +2198,10 @@
         <v>10</v>
       </c>
       <c r="E30" t="n">
-        <v>0.5835171995337922</v>
+        <v>0.439597353161678</v>
       </c>
       <c r="F30" t="n">
-        <v>0.3273950213427199</v>
+        <v>0.25</v>
       </c>
       <c r="G30" t="n">
         <v>37</v>
@@ -2209,52 +2209,52 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>S003,S004,S005,S007,S008,S009,S011,S015 | S001,S002,S010,S012,S013,S014 | S006</t>
+          <t>S002,S003,S004,S005,S006,S007,S008,S009,S013,S015 | S001,S010,S011,S012,S014</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E31" t="n">
-        <v>0.6726183409005074</v>
+        <v>0.4537065876595903</v>
       </c>
       <c r="F31" t="n">
-        <v>0.5514186250028194</v>
+        <v>0.325</v>
       </c>
       <c r="G31" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>S003,S004,S005,S006,S007,S008,S009,S015 | S001,S002,S010,S012,S013,S014 | S011</t>
+          <t>S002,S003,S004,S005,S007,S008,S009,S013,S015 | S001,S006,S010,S011,S012,S014</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D32" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E32" t="n">
-        <v>0.6884774111878296</v>
+        <v>0.3943837640185381</v>
       </c>
       <c r="F32" t="n">
-        <v>0.6366415789123422</v>
+        <v>0.175</v>
       </c>
       <c r="G32" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="33">
@@ -2263,23 +2263,23 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>S003,S004,S005,S007,S008,S009,S015 | S002,S010,S011,S012,S013,S014 | S001,S006</t>
+          <t>S001,S002,S003,S004,S005,S007,S008,S009,S010,S012,S013,S014,S015 | S006 | S011</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D33" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E33" t="n">
-        <v>0.563230897084078</v>
+        <v>1.30336459111859</v>
       </c>
       <c r="F33" t="n">
-        <v>0.24937421679075</v>
+        <v>1.176461856585244</v>
       </c>
       <c r="G33" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
     <row r="34">
@@ -2288,23 +2288,23 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>S003,S004,S005,S007,S008,S009,S011,S015 | S002,S006,S010,S012,S013,S014 | S001</t>
+          <t>S001,S002,S004,S005,S008,S009,S010,S012,S013,S014 | S003,S007,S011,S015 | S006</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D34" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E34" t="n">
-        <v>0.6248325892739741</v>
+        <v>0.7843651622552725</v>
       </c>
       <c r="F34" t="n">
-        <v>0.367848474239054</v>
+        <v>0.7772145778354906</v>
       </c>
       <c r="G34" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35">
@@ -2313,23 +2313,23 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>S003,S004,S005,S007,S008,S009,S015 | S001,S002,S010,S011,S012,S013,S014 | S006</t>
+          <t>S001,S002,S004,S005,S006,S008,S009,S010,S012,S013,S014 | S003,S007,S015 | S011</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D35" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E35" t="n">
-        <v>0.660598067017912</v>
+        <v>0.8343407509702256</v>
       </c>
       <c r="F35" t="n">
-        <v>0.5488624600025036</v>
+        <v>0.93189994098079</v>
       </c>
       <c r="G35" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="36">
@@ -2338,23 +2338,23 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>S003,S004,S005,S007,S008,S009,S015 | S002,S006,S010,S011,S012,S013,S014 | S001</t>
+          <t>S002,S003,S004,S005,S007,S008,S009,S010,S011,S012,S013,S014,S015 | S001 | S006</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D36" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E36" t="n">
-        <v>0.608847382674176</v>
+        <v>1.22333044924975</v>
       </c>
       <c r="F36" t="n">
-        <v>0.3273950213427199</v>
+        <v>0.8683677216479202</v>
       </c>
       <c r="G36" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="37">
@@ -2363,23 +2363,23 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>S003,S004,S005,S006,S007,S008,S009,S015 | S002,S010,S012,S013,S014 | S001,S011</t>
+          <t>S002,S003,S004,S005,S006,S007,S008,S009,S010,S012,S013,S014,S015 | S001 | S011</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D37" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E37" t="n">
-        <v>0.5998298505057754</v>
+        <v>1.238582942784785</v>
       </c>
       <c r="F37" t="n">
-        <v>0.4077376607575023</v>
+        <v>0.9547578226964154</v>
       </c>
       <c r="G37" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="38">
@@ -2388,23 +2388,23 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>S003,S004,S005,S007,S008,S009,S015 | S001,S002,S006,S010,S012,S013,S014 | S011</t>
+          <t>S001,S002,S004,S005,S008,S009,S010,S012,S013,S014 | S003,S006,S007,S015 | S011</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D38" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E38" t="n">
-        <v>0.6729950210450741</v>
+        <v>0.7918807153637663</v>
       </c>
       <c r="F38" t="n">
-        <v>0.6322084308200896</v>
+        <v>0.8056441522161009</v>
       </c>
       <c r="G38" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="39">
@@ -2413,23 +2413,23 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>S003,S004,S005,S007,S008,S009,S015 | S002,S010,S012,S013,S014 | S001,S006,S011</t>
+          <t>S002,S004,S005,S006,S008,S009,S010,S012,S013,S014 | S003,S007,S011,S015 | S001</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D39" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E39" t="n">
-        <v>0.5318048242264147</v>
+        <v>0.7088777559228913</v>
       </c>
       <c r="F39" t="n">
-        <v>0.2549509756796393</v>
+        <v>0.5162969107015846</v>
       </c>
       <c r="G39" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="40">
@@ -2438,23 +2438,23 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>S003,S004,S005,S007,S008,S009,S015 | S001,S002,S010,S012,S013,S014 | S006,S011</t>
+          <t>S002,S004,S005,S008,S009,S010,S012,S013,S014 | S001,S003,S007,S011,S015 | S006</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D40" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E40" t="n">
-        <v>0.6224964490507595</v>
+        <v>0.7102203843604716</v>
       </c>
       <c r="F40" t="n">
-        <v>0.4687083314813169</v>
+        <v>0.5556527692723217</v>
       </c>
       <c r="G40" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="41">
@@ -2463,27 +2463,2052 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>S003,S004,S005,S007,S008,S009,S015 | S002,S006,S010,S012,S013,S014 | S001,S011</t>
+          <t>S002,S004,S005,S006,S008,S009,S010,S012,S013,S014 | S001,S003,S007,S015 | S011</t>
         </is>
       </c>
       <c r="C41" t="n">
+        <v>7</v>
+      </c>
+      <c r="D41" t="n">
+        <v>7</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.7525320915113256</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.6682533202311829</v>
+      </c>
+      <c r="G41" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>3</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>S001,S002,S003,S004,S005,S007,S008,S009,S011,S013,S015 | S010,S012,S014 | S006</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>7</v>
+      </c>
+      <c r="D42" t="n">
+        <v>7</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.9684686980222232</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1.017503071248436</v>
+      </c>
+      <c r="G42" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>3</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>S001,S002,S003,S004,S005,S006,S007,S008,S009,S013,S015 | S010,S012,S014 | S011</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>7</v>
+      </c>
+      <c r="D43" t="n">
+        <v>7</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.9848894062606174</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1.099857945372947</v>
+      </c>
+      <c r="G43" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>3</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>S002,S003,S004,S005,S007,S008,S009,S010,S012,S013,S014,S015 | S001,S006 | S011</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>7</v>
+      </c>
+      <c r="D44" t="n">
+        <v>7</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1.177705628260265</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.8251893722049504</v>
+      </c>
+      <c r="G44" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>3</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>S001,S002,S004,S005,S008,S009,S013 | S003,S007,S010,S011,S012,S014,S015 | S006</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>7</v>
+      </c>
+      <c r="D45" t="n">
+        <v>8</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.6444302635727819</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.6133922073192649</v>
+      </c>
+      <c r="G45" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>3</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>S001,S002,S004,S005,S006,S008,S009,S013 | S003,S007,S010,S012,S014,S015 | S011</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>7</v>
+      </c>
+      <c r="D46" t="n">
+        <v>8</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.6607713230017489</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.7514569182594568</v>
+      </c>
+      <c r="G46" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>S002,S004,S005,S008,S009,S010,S012,S013,S014 | S003,S006,S007,S011,S015 | S001</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>7</v>
+      </c>
+      <c r="D47" t="n">
+        <v>8</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.6695268161591399</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.3852758751855611</v>
+      </c>
+      <c r="G47" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>3</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>S001,S002,S004,S005,S008,S009,S013 | S003,S006,S007,S010,S012,S014,S015 | S011</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>7</v>
+      </c>
+      <c r="D48" t="n">
+        <v>9</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.6596790970234439</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.6682533202311829</v>
+      </c>
+      <c r="G48" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>3</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>S001,S002,S004,S005,S008,S009,S011,S013 | S003,S007,S010,S012,S014,S015 | S006</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>7</v>
+      </c>
+      <c r="D49" t="n">
+        <v>10</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.6452825562427983</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.6597821610198323</v>
+      </c>
+      <c r="G49" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>3</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>S001,S002,S004,S005,S006,S008,S009,S013 | S003,S007,S011,S015 | S010,S012,S014</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>8</v>
+      </c>
+      <c r="D50" t="n">
+        <v>8</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.3944926961545641</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.6889756889760335</v>
+      </c>
+      <c r="G50" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>3</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>S002,S004,S005,S008,S009,S010,S012,S013,S014 | S003,S007,S011,S015 | S001,S006</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>8</v>
+      </c>
+      <c r="D51" t="n">
+        <v>8</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.6365681361137456</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.3548767391644597</v>
+      </c>
+      <c r="G51" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>3</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>S002,S004,S005,S008,S009,S010,S012,S013,S014 | S001,S003,S006,S007,S015 | S011</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>8</v>
+      </c>
+      <c r="D52" t="n">
+        <v>8</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.7202946245960947</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.629235647432661</v>
+      </c>
+      <c r="G52" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>3</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>S001,S002,S004,S005,S008,S009,S010,S012,S013,S014 | S003,S007,S015 | S006,S011</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>8</v>
+      </c>
+      <c r="D53" t="n">
+        <v>8</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.762423691678611</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.758905461833027</v>
+      </c>
+      <c r="G53" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>3</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>S001,S002,S004,S005,S008,S009,S010,S011,S012,S013,S014 | S003,S007,S015 | S006</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>8</v>
+      </c>
+      <c r="D54" t="n">
+        <v>8</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.8172242886646404</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.84483726243579</v>
+      </c>
+      <c r="G54" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>3</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>S002,S003,S004,S005,S007,S008,S009,S010,S012,S013,S014,S015 | S001 | S006,S011</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>8</v>
+      </c>
+      <c r="D55" t="n">
+        <v>8</v>
+      </c>
+      <c r="E55" t="n">
+        <v>1.174831576900369</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.783222509891027</v>
+      </c>
+      <c r="G55" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>3</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>S002,S003,S004,S005,S007,S008,S009,S010,S012,S013,S014,S015 | S001,S011 | S006</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>8</v>
+      </c>
+      <c r="D56" t="n">
+        <v>8</v>
+      </c>
+      <c r="E56" t="n">
+        <v>1.176616145809798</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.7992183681572889</v>
+      </c>
+      <c r="G56" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>3</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>S001,S002,S004,S005,S008,S009,S013 | S003,S006,S007,S011,S015 | S010,S012,S014</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>8</v>
+      </c>
+      <c r="D57" t="n">
+        <v>9</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.3527066177058506</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.5681659088681755</v>
+      </c>
+      <c r="G57" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>3</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>S002,S004,S005,S006,S008,S009,S013 | S003,S007,S010,S011,S012,S014,S015 | S001</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>8</v>
+      </c>
+      <c r="D58" t="n">
+        <v>9</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.5812285827153243</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.3386554296036017</v>
+      </c>
+      <c r="G58" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>3</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>S002,S004,S005,S008,S009,S013 | S001,S003,S007,S010,S011,S012,S014,S015 | S006</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>8</v>
+      </c>
+      <c r="D59" t="n">
+        <v>9</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.6652792749448064</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.5779814010848445</v>
+      </c>
+      <c r="G59" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>3</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>S002,S004,S005,S006,S008,S009,S013 | S001,S003,S007,S010,S012,S014,S015 | S011</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>8</v>
+      </c>
+      <c r="D60" t="n">
+        <v>9</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.6670237355503458</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.629235647432661</v>
+      </c>
+      <c r="G60" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>3</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>S001,S002,S004,S005,S006,S008,S009,S011,S013 | S003,S007,S015 | S010,S012,S014</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>8</v>
+      </c>
+      <c r="D61" t="n">
+        <v>10</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.4318689679577531</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.758905461833027</v>
+      </c>
+      <c r="G61" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>3</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>S002,S004,S005,S008,S009,S013 | S003,S006,S007,S010,S011,S012,S014,S015 | S001</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>8</v>
+      </c>
+      <c r="D62" t="n">
+        <v>10</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.5926148337595848</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.3127499000799201</v>
+      </c>
+      <c r="G62" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>3</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>S001,S002,S004,S005,S008,S009,S011,S013 | S003,S006,S007,S015 | S010,S012,S014</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>8</v>
+      </c>
+      <c r="D63" t="n">
+        <v>11</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.3837208399531436</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.62474994997999</v>
+      </c>
+      <c r="G63" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>3</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>S002,S004,S005,S006,S008,S009,S011,S013 | S003,S007,S010,S012,S014,S015 | S001</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>8</v>
+      </c>
+      <c r="D64" t="n">
+        <v>11</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.5785581713621581</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.3852758751855611</v>
+      </c>
+      <c r="G64" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>3</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>S002,S004,S005,S008,S009,S011,S013 | S001,S003,S007,S010,S012,S014,S015 | S006</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>8</v>
+      </c>
+      <c r="D65" t="n">
+        <v>11</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.6536485998859778</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.5556527692723217</v>
+      </c>
+      <c r="G65" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>3</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>S002,S004,S005,S008,S009,S011,S013 | S003,S006,S007,S010,S012,S014,S015 | S001</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>8</v>
+      </c>
+      <c r="D66" t="n">
         <v>12</v>
       </c>
-      <c r="D41" t="n">
+      <c r="E66" t="n">
+        <v>0.5831368965790172</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0.3127499000799201</v>
+      </c>
+      <c r="G66" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>3</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>S002,S004,S005,S006,S008,S009,S013 | S001,S003,S007,S011,S015 | S010,S012,S014</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>9</v>
+      </c>
+      <c r="D67" t="n">
+        <v>9</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.32106867759908</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0.4707042595940683</v>
+      </c>
+      <c r="G67" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>3</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>S002,S004,S005,S008,S009,S010,S012,S013,S014 | S001,S003,S007,S015 | S006,S011</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>9</v>
+      </c>
+      <c r="D68" t="n">
+        <v>9</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.6798930467902773</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.4883006246156152</v>
+      </c>
+      <c r="G68" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>3</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>S002,S004,S005,S006,S008,S009,S010,S012,S013,S014 | S003,S007,S015 | S001,S011</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>9</v>
+      </c>
+      <c r="D69" t="n">
+        <v>9</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.6875792108648074</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.5135659646043534</v>
+      </c>
+      <c r="G69" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>3</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>S002,S004,S005,S008,S009,S010,S011,S012,S013,S014 | S001,S003,S007,S015 | S006</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>9</v>
+      </c>
+      <c r="D70" t="n">
+        <v>9</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.7352554591867239</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0.5779814010848445</v>
+      </c>
+      <c r="G70" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>3</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>S002,S004,S005,S006,S008,S009,S010,S011,S012,S013,S014 | S003,S007,S015 | S001</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>9</v>
+      </c>
+      <c r="D71" t="n">
+        <v>9</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0.7422521017604908</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0.5923997805536393</v>
+      </c>
+      <c r="G71" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>3</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>S002,S003,S004,S005,S006,S007,S008,S009,S011,S013,S015 | S010,S012,S014 | S001</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>9</v>
+      </c>
+      <c r="D72" t="n">
+        <v>9</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.896839496788973</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0.783222509891027</v>
+      </c>
+      <c r="G72" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>3</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>S001,S002,S003,S004,S005,S007,S008,S009,S013,S015 | S010,S012,S014 | S006,S011</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>9</v>
+      </c>
+      <c r="D73" t="n">
+        <v>9</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.9160609459143347</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.9369164850721754</v>
+      </c>
+      <c r="G73" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>3</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>S001,S002,S003,S004,S005,S007,S008,S009,S013,S015 | S010,S011,S012,S014 | S006</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>9</v>
+      </c>
+      <c r="D74" t="n">
+        <v>9</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.9278513720890625</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.9414085191881365</v>
+      </c>
+      <c r="G74" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>3</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>S001,S002,S003,S004,S005,S007,S008,S009,S013,S015 | S006,S010,S012,S014 | S011</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>9</v>
+      </c>
+      <c r="D75" t="n">
+        <v>9</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.932173779680295</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0.9547578226964154</v>
+      </c>
+      <c r="G75" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>3</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>S002,S004,S005,S008,S009,S013 | S003,S007,S010,S011,S012,S014,S015 | S001,S006</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>9</v>
+      </c>
+      <c r="D76" t="n">
+        <v>10</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.5237762690258851</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0.1571225636247067</v>
+      </c>
+      <c r="G76" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>3</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>S001,S002,S004,S005,S008,S009,S013 | S003,S007,S010,S012,S014,S015 | S006,S011</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>9</v>
+      </c>
+      <c r="D77" t="n">
+        <v>10</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.596311775635129</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.5681659088681755</v>
+      </c>
+      <c r="G77" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>3</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>S002,S004,S005,S008,S009,S010,S012,S013,S014 | S003,S006,S007,S015 | S001,S011</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>9</v>
+      </c>
+      <c r="D78" t="n">
+        <v>10</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.6438170231245952</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0.3588175023601831</v>
+      </c>
+      <c r="G78" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>3</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>S002,S004,S005,S008,S009,S013 | S001,S003,S006,S007,S010,S012,S014,S015 | S011</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>9</v>
+      </c>
+      <c r="D79" t="n">
+        <v>10</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.6819440243655424</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0.6682533202311829</v>
+      </c>
+      <c r="G79" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>3</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>S002,S004,S005,S008,S009,S010,S011,S012,S013,S014 | S003,S006,S007,S015 | S001</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>9</v>
+      </c>
+      <c r="D80" t="n">
+        <v>10</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.699035102092187</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.4461642074393686</v>
+      </c>
+      <c r="G80" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>3</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>S002,S004,S005,S006,S008,S009,S011,S013 | S001,S003,S007,S015 | S010,S012,S014</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>9</v>
+      </c>
+      <c r="D81" t="n">
+        <v>11</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0.342829665548179</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0.4883006246156152</v>
+      </c>
+      <c r="G81" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>3</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>S002,S004,S005,S008,S009,S011,S013 | S003,S007,S010,S012,S014,S015 | S001,S006</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>9</v>
+      </c>
+      <c r="D82" t="n">
+        <v>12</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0.5169344016574635</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0.2038688303787511</v>
+      </c>
+      <c r="G82" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>3</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>S002,S004,S005,S008,S009,S013 | S001,S003,S006,S007,S011,S015 | S010,S012,S014</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>10</v>
+      </c>
+      <c r="D83" t="n">
+        <v>10</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0.3056661339134161</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0.4883006246156152</v>
+      </c>
+      <c r="G83" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>3</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>S001,S002,S004,S005,S008,S009,S013 | S003,S007,S011,S015 | S006,S010,S012,S014</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>10</v>
+      </c>
+      <c r="D84" t="n">
+        <v>10</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0.323069309394931</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0.5162969107015846</v>
+      </c>
+      <c r="G84" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>3</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>S001,S002,S004,S005,S006,S008,S009,S013 | S003,S007,S015 | S010,S011,S012,S014</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>10</v>
+      </c>
+      <c r="D85" t="n">
+        <v>10</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0.378716486636757</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0.674536878161602</v>
+      </c>
+      <c r="G85" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>3</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>S002,S004,S005,S008,S009,S010,S012,S013,S014 | S003,S007,S015 | S001,S006,S011</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>10</v>
+      </c>
+      <c r="D86" t="n">
+        <v>10</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0.6160355403293722</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0.3741657386773941</v>
+      </c>
+      <c r="G86" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>3</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>S002,S004,S005,S008,S009,S010,S011,S012,S013,S014 | S003,S007,S015 | S001,S006</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>10</v>
+      </c>
+      <c r="D87" t="n">
+        <v>10</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0.6705417250093718</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0.4398153021439795</v>
+      </c>
+      <c r="G87" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>3</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>S002,S003,S004,S005,S007,S008,S009,S011,S013,S015 | S010,S012,S014 | S001,S006</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>10</v>
+      </c>
+      <c r="D88" t="n">
+        <v>10</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0.8288571786340329</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0.6454165321712794</v>
+      </c>
+      <c r="G88" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>3</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>S001,S002,S004,S005,S008,S009,S013 | S003,S006,S007,S015 | S010,S011,S012,S014</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>10</v>
+      </c>
+      <c r="D89" t="n">
+        <v>11</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0.3289078160249714</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0.5350233639758174</v>
+      </c>
+      <c r="G89" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>3</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>S002,S004,S005,S006,S008,S009,S013 | S003,S007,S010,S012,S014,S015 | S001,S011</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>10</v>
+      </c>
+      <c r="D90" t="n">
+        <v>11</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0.5313382679762447</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0.2942150573984955</v>
+      </c>
+      <c r="G90" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>3</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>S002,S004,S005,S008,S009,S013 | S001,S003,S007,S010,S012,S014,S015 | S006,S011</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>10</v>
+      </c>
+      <c r="D91" t="n">
+        <v>11</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0.6121064169433703</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0.4883006246156152</v>
+      </c>
+      <c r="G91" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>3</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>S002,S004,S005,S008,S009,S011,S013 | S001,S003,S006,S007,S015 | S010,S012,S014</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>10</v>
+      </c>
+      <c r="D92" t="n">
+        <v>12</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0.3159624597028518</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0.4707042595940683</v>
+      </c>
+      <c r="G92" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>3</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>S001,S002,S004,S005,S008,S009,S011,S013 | S003,S007,S015 | S006,S010,S012,S014</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>10</v>
+      </c>
+      <c r="D93" t="n">
+        <v>12</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0.3622662007090075</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0.5923997805536393</v>
+      </c>
+      <c r="G93" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>3</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>S002,S004,S005,S008,S009,S013 | S003,S006,S007,S010,S012,S014,S015 | S001,S011</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>10</v>
+      </c>
+      <c r="D94" t="n">
+        <v>12</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0.5400580840800876</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0.2298097038856279</v>
+      </c>
+      <c r="G94" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>3</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>S002,S004,S005,S006,S008,S009,S013 | S003,S007,S011,S015 | S001,S010,S012,S014</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>11</v>
+      </c>
+      <c r="D95" t="n">
+        <v>11</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0.2493339429438817</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0.2844951669185261</v>
+      </c>
+      <c r="G95" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>3</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>S002,S004,S005,S008,S009,S013 | S001,S003,S007,S011,S015 | S006,S010,S012,S014</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>11</v>
+      </c>
+      <c r="D96" t="n">
+        <v>11</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0.2502378798362005</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0.3127499000799201</v>
+      </c>
+      <c r="G96" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>3</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>S002,S004,S005,S006,S008,S009,S013 | S001,S003,S007,S015 | S010,S011,S012,S014</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>11</v>
+      </c>
+      <c r="D97" t="n">
+        <v>11</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0.2875189880789476</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0.3996091840786445</v>
+      </c>
+      <c r="G97" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>3</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>S002,S003,S004,S005,S007,S008,S009,S011,S013,S015 | S006,S010,S012,S014 | S001</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>11</v>
+      </c>
+      <c r="D98" t="n">
+        <v>11</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0.8426287490428108</v>
+      </c>
+      <c r="F98" t="n">
+        <v>0.6187184335382291</v>
+      </c>
+      <c r="G98" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>3</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>S002,S003,S004,S005,S006,S007,S008,S009,S013,S015 | S010,S012,S014 | S001,S011</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>11</v>
+      </c>
+      <c r="D99" t="n">
+        <v>11</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0.8449554790505208</v>
+      </c>
+      <c r="F99" t="n">
+        <v>0.711732042274338</v>
+      </c>
+      <c r="G99" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>3</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>S002,S003,S004,S005,S006,S007,S008,S009,S013,S015 | S010,S011,S012,S014 | S001</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>11</v>
+      </c>
+      <c r="D100" t="n">
+        <v>11</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0.8552741976334196</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0.6997767501139202</v>
+      </c>
+      <c r="G100" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>3</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>S002,S003,S004,S005,S007,S008,S009,S011,S013,S015 | S001,S010,S012,S014 | S006</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>11</v>
+      </c>
+      <c r="D101" t="n">
+        <v>11</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0.8632963247852372</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0.6773108592072034</v>
+      </c>
+      <c r="G101" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>3</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>S002,S003,S004,S005,S006,S007,S008,S009,S013,S015 | S001,S010,S012,S014 | S011</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>11</v>
+      </c>
+      <c r="D102" t="n">
+        <v>11</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0.880222174026323</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0.7687245930760899</v>
+      </c>
+      <c r="G102" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>3</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>S002,S004,S005,S008,S009,S013 | S003,S006,S007,S011,S015 | S001,S010,S012,S014</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>11</v>
+      </c>
+      <c r="D103" t="n">
+        <v>12</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0.204277985534959</v>
+      </c>
+      <c r="F103" t="n">
+        <v>0.1159202311936963</v>
+      </c>
+      <c r="G103" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>3</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>S002,S004,S005,S008,S009,S013 | S003,S007,S010,S012,S014,S015 | S001,S006,S011</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>11</v>
+      </c>
+      <c r="D104" t="n">
+        <v>12</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0.4720789831244169</v>
+      </c>
+      <c r="F104" t="n">
+        <v>0.1159202311936963</v>
+      </c>
+      <c r="G104" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>3</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>S002,S004,S005,S008,S009,S011,S013 | S001,S003,S007,S015 | S006,S010,S012,S014</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>11</v>
+      </c>
+      <c r="D105" t="n">
         <v>13</v>
       </c>
-      <c r="E41" t="n">
-        <v>0.5737570601269734</v>
-      </c>
-      <c r="F41" t="n">
-        <v>0.2761340254296815</v>
-      </c>
-      <c r="G41" t="n">
+      <c r="E105" t="n">
+        <v>0.2702642848901696</v>
+      </c>
+      <c r="F105" t="n">
+        <v>0.3127499000799201</v>
+      </c>
+      <c r="G105" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>3</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>S002,S004,S005,S006,S008,S009,S011,S013 | S003,S007,S015 | S001,S010,S012,S014</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>11</v>
+      </c>
+      <c r="D106" t="n">
+        <v>13</v>
+      </c>
+      <c r="E106" t="n">
+        <v>0.2912629672805466</v>
+      </c>
+      <c r="F106" t="n">
+        <v>0.3741657386773941</v>
+      </c>
+      <c r="G106" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>3</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>S002,S004,S005,S008,S009,S011,S013 | S003,S006,S007,S015 | S001,S010,S012,S014</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>11</v>
+      </c>
+      <c r="D107" t="n">
+        <v>14</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0.2373807133163821</v>
+      </c>
+      <c r="F107" t="n">
+        <v>0.1968501968502953</v>
+      </c>
+      <c r="G107" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>3</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>S002,S004,S005,S008,S009,S013 | S003,S007,S011,S015 | S001,S006,S010,S012,S014</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>12</v>
+      </c>
+      <c r="D108" t="n">
+        <v>12</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0.1802385233231563</v>
+      </c>
+      <c r="F108" t="n">
+        <v>0.2038688303787511</v>
+      </c>
+      <c r="G108" t="n">
         <v>39</v>
       </c>
     </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>3</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>S002,S004,S005,S008,S009,S013 | S001,S003,S006,S007,S015 | S010,S011,S012,S014</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>12</v>
+      </c>
+      <c r="D109" t="n">
+        <v>12</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0.26266054429609</v>
+      </c>
+      <c r="F109" t="n">
+        <v>0.3996091840786445</v>
+      </c>
+      <c r="G109" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>3</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>S001,S002,S004,S005,S008,S009,S013 | S003,S007,S015 | S006,S010,S011,S012,S014</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>12</v>
+      </c>
+      <c r="D110" t="n">
+        <v>12</v>
+      </c>
+      <c r="E110" t="n">
+        <v>0.3101592579087162</v>
+      </c>
+      <c r="F110" t="n">
+        <v>0.5135659646043534</v>
+      </c>
+      <c r="G110" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>3</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>S002,S003,S004,S005,S007,S008,S009,S013,S015 | S010,S012,S014 | S001,S006,S011</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>12</v>
+      </c>
+      <c r="D111" t="n">
+        <v>12</v>
+      </c>
+      <c r="E111" t="n">
+        <v>0.7776114032566125</v>
+      </c>
+      <c r="F111" t="n">
+        <v>0.5860354084865521</v>
+      </c>
+      <c r="G111" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>3</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>S002,S003,S004,S005,S007,S008,S009,S013,S015 | S010,S011,S012,S014 | S001,S006</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>12</v>
+      </c>
+      <c r="D112" t="n">
+        <v>12</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0.7862572030654705</v>
+      </c>
+      <c r="F112" t="n">
+        <v>0.5564957322388016</v>
+      </c>
+      <c r="G112" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>3</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>S002,S003,S004,S005,S007,S008,S009,S013,S015 | S001,S006,S010,S012,S014 | S011</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>12</v>
+      </c>
+      <c r="D113" t="n">
+        <v>12</v>
+      </c>
+      <c r="E113" t="n">
+        <v>0.8338471727114213</v>
+      </c>
+      <c r="F113" t="n">
+        <v>0.6793839120850595</v>
+      </c>
+      <c r="G113" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>3</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>S002,S004,S005,S008,S009,S011,S013 | S003,S007,S015 | S001,S006,S010,S012,S014</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>12</v>
+      </c>
+      <c r="D114" t="n">
+        <v>14</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0.2261179551306388</v>
+      </c>
+      <c r="F114" t="n">
+        <v>0.2893959225697556</v>
+      </c>
+      <c r="G114" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>3</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>S002,S004,S005,S008,S009,S013 | S001,S003,S007,S015 | S006,S010,S011,S012,S014</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>13</v>
+      </c>
+      <c r="D115" t="n">
+        <v>13</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0.2149985254321827</v>
+      </c>
+      <c r="F115" t="n">
+        <v>0.2298097038856279</v>
+      </c>
+      <c r="G115" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>3</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>S002,S004,S005,S006,S008,S009,S013 | S003,S007,S015 | S001,S010,S011,S012,S014</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>13</v>
+      </c>
+      <c r="D116" t="n">
+        <v>13</v>
+      </c>
+      <c r="E116" t="n">
+        <v>0.241223386502234</v>
+      </c>
+      <c r="F116" t="n">
+        <v>0.3216170082567152</v>
+      </c>
+      <c r="G116" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>3</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>S002,S003,S004,S005,S007,S008,S009,S013,S015 | S006,S010,S012,S014 | S001,S011</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>13</v>
+      </c>
+      <c r="D117" t="n">
+        <v>13</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.7897310833142034</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.541121520547834</v>
+      </c>
+      <c r="G117" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>3</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>S002,S003,S004,S005,S007,S008,S009,S013,S015 | S006,S010,S011,S012,S014 | S001</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>13</v>
+      </c>
+      <c r="D118" t="n">
+        <v>13</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.8032699870996026</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.541121520547834</v>
+      </c>
+      <c r="G118" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>3</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>S002,S003,S004,S005,S007,S008,S009,S013,S015 | S001,S010,S012,S014 | S006,S011</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>13</v>
+      </c>
+      <c r="D119" t="n">
+        <v>13</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.8091577096764111</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.5860354084865521</v>
+      </c>
+      <c r="G119" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>3</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>S002,S003,S004,S005,S007,S008,S009,S013,S015 | S001,S010,S011,S012,S014 | S006</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>13</v>
+      </c>
+      <c r="D120" t="n">
+        <v>13</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.8274637927712226</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.627743976474486</v>
+      </c>
+      <c r="G120" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>3</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>S002,S004,S005,S008,S009,S013 | S003,S006,S007,S015 | S001,S010,S011,S012,S014</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>13</v>
+      </c>
+      <c r="D121" t="n">
+        <v>14</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.1836504990559732</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.1380670127148408</v>
+      </c>
+      <c r="G121" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>3</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>S002,S004,S005,S008,S009,S013 | S003,S007,S015 | S001,S006,S010,S011,S012,S014</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>14</v>
+      </c>
+      <c r="D122" t="n">
+        <v>14</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.1803622162309819</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.2844951669185261</v>
+      </c>
+      <c r="G122" t="n">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G41"/>
+  <autoFilter ref="A1:G122"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2494,7 +4519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2515,7 +4540,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>S003,S004,S005,S007,S008,S009,S015</t>
+          <t>S002,S004,S005,S008,S009,S013</t>
         </is>
       </c>
     </row>
@@ -2525,7 +4550,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>S002,S010,S012,S013,S014</t>
+          <t>S003,S007,S015</t>
         </is>
       </c>
     </row>
@@ -2535,7 +4560,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S010,S012,S014</t>
         </is>
       </c>
     </row>
@@ -2545,7 +4570,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>S006</t>
+          <t>S001</t>
         </is>
       </c>
     </row>
@@ -2555,12 +4580,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>S006</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>S011</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B6"/>
+  <autoFilter ref="A1:B7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>